--- a/framework/hcv_vaccine_framework.xlsx
+++ b/framework/hcv_vaccine_framework.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farah.houdroge\Documents\GitHub\hcv-vaccine\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62F938B-168F-43C2-84F0-85FB1F3A3E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225ED5F5-6C5E-4399-A53C-7AB9FFBD0A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -53173,7 +53173,7 @@
           <x14:formula1>
             <xm:f>'Population types'!$A$2:$A$9999</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:E1048576</xm:sqref>
+          <xm:sqref>D4:E1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
